--- a/ROSA_vitaSPEC/Results/test_pretraitements/C14.0/CAROT_/CAROT_Resultats_C14.0_moy_ADJR2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/C14.0/CAROT_/CAROT_Resultats_C14.0_moy_ADJR2.xlsx
@@ -1,21 +1,220 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\C14.0\CAROT_\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+  <si>
+    <t>Pretraitement</t>
+  </si>
+  <si>
+    <t>LV0_ADJR2</t>
+  </si>
+  <si>
+    <t>LV1_ADJR2</t>
+  </si>
+  <si>
+    <t>LV2_ADJR2</t>
+  </si>
+  <si>
+    <t>LV3_ADJR2</t>
+  </si>
+  <si>
+    <t>LV4_ADJR2</t>
+  </si>
+  <si>
+    <t>LV5_ADJR2</t>
+  </si>
+  <si>
+    <t>LV6_ADJR2</t>
+  </si>
+  <si>
+    <t>LV7_ADJR2</t>
+  </si>
+  <si>
+    <t>LV8_ADJR2</t>
+  </si>
+  <si>
+    <t>LV9_ADJR2</t>
+  </si>
+  <si>
+    <t>LV10_ADJR2</t>
+  </si>
+  <si>
+    <t>LV11_ADJR2</t>
+  </si>
+  <si>
+    <t>LV12_ADJR2</t>
+  </si>
+  <si>
+    <t>LV13_ADJR2</t>
+  </si>
+  <si>
+    <t>LV14_ADJR2</t>
+  </si>
+  <si>
+    <t>LV15_ADJR2</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1000,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+  </si>
+  <si>
+    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(1,3,5)_</t>
+  </si>
+  <si>
+    <t>adj_snv_sder_c(2,3,15)_</t>
+  </si>
+  <si>
+    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,11 +262,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -109,7 +316,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -141,9 +348,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -175,6 +383,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,337 +559,299 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Pretraitement</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>LV0_ADJR2</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>LV1_ADJR2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>LV2_ADJR2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>LV3_ADJR2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>LV4_ADJR2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>LV5_ADJR2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LV6_ADJR2</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LV7_ADJR2</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>LV8_ADJR2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>LV9_ADJR2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>LV10_ADJR2</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>LV11_ADJR2</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>LV12_ADJR2</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LV13_ADJR2</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>LV14_ADJR2</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>LV15_ADJR2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1000,1)_snv_</t>
-        </is>
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C2">
-        <v>-0.0005725491135705661</v>
+        <v>-5.7254911357056614E-4</v>
       </c>
       <c r="D2">
-        <v>0.007457131865510247</v>
+        <v>7.4571318655102473E-3</v>
       </c>
       <c r="E2">
-        <v>0.02036420461759758</v>
+        <v>2.0364204617597581E-2</v>
       </c>
       <c r="F2">
-        <v>0.06701597977993269</v>
+        <v>6.7015979779932691E-2</v>
       </c>
       <c r="G2">
-        <v>0.1079149758598519</v>
+        <v>0.10791497585985189</v>
       </c>
       <c r="H2">
         <v>0.1874839225344796</v>
       </c>
       <c r="I2">
-        <v>0.2712601099898546</v>
+        <v>0.27126010998985461</v>
       </c>
       <c r="J2">
-        <v>0.3234020475665126</v>
+        <v>0.32340204756651258</v>
       </c>
       <c r="K2">
-        <v>0.3424412766539036</v>
+        <v>0.34244127665390361</v>
       </c>
       <c r="L2">
-        <v>0.3714592371328256</v>
+        <v>0.37145923713282558</v>
       </c>
       <c r="M2">
-        <v>0.3788056126929942</v>
+        <v>0.37880561269299418</v>
       </c>
       <c r="N2">
-        <v>0.3843578783464842</v>
+        <v>0.38435787834648422</v>
       </c>
       <c r="O2">
-        <v>0.3830108765172349</v>
+        <v>0.38301087651723492</v>
       </c>
       <c r="P2">
-        <v>0.3691385438346912</v>
+        <v>0.36913854383469119</v>
       </c>
       <c r="Q2">
-        <v>0.3335581590601867</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.33355815906018671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C3">
-        <v>-0.009151906532973458</v>
+        <v>-9.1519065329734584E-3</v>
       </c>
       <c r="D3">
-        <v>-0.005471349293532287</v>
+        <v>-5.4713492935322874E-3</v>
       </c>
       <c r="E3">
-        <v>0.004514442532426718</v>
+        <v>4.5144425324267178E-3</v>
       </c>
       <c r="F3">
-        <v>0.06668326882810184</v>
+        <v>6.6683268828101841E-2</v>
       </c>
       <c r="G3">
         <v>0.1911128841752906</v>
       </c>
       <c r="H3">
-        <v>0.2474140679622158</v>
+        <v>0.24741406796221579</v>
       </c>
       <c r="I3">
-        <v>0.2673743103745808</v>
+        <v>0.26737431037458081</v>
       </c>
       <c r="J3">
         <v>0.3008815263135175</v>
       </c>
       <c r="K3">
-        <v>0.3174152574809184</v>
+        <v>0.31741525748091842</v>
       </c>
       <c r="L3">
-        <v>0.3462567150978172</v>
+        <v>0.34625671509781719</v>
       </c>
       <c r="M3">
-        <v>0.3412072695870736</v>
+        <v>0.34120726958707359</v>
       </c>
       <c r="N3">
-        <v>0.3502032110330314</v>
+        <v>0.35020321103303143</v>
       </c>
       <c r="O3">
-        <v>0.3277656955776947</v>
+        <v>0.32776569557769469</v>
       </c>
       <c r="P3">
-        <v>0.2863257520335566</v>
+        <v>0.28632575203355659</v>
       </c>
       <c r="Q3">
-        <v>0.2491003333457742</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.24910033334577419</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C4">
-        <v>-0.01181781241221679</v>
+        <v>-1.1817812412216791E-2</v>
       </c>
       <c r="D4">
-        <v>-0.03525894149168415</v>
+        <v>-3.5258941491684147E-2</v>
       </c>
       <c r="E4">
-        <v>-0.004152523173645472</v>
+        <v>-4.1525231736454721E-3</v>
       </c>
       <c r="F4">
-        <v>-0.006190117088114375</v>
+        <v>-6.1901170881143754E-3</v>
       </c>
       <c r="G4">
-        <v>0.02988681487852724</v>
+        <v>2.9886814878527242E-2</v>
       </c>
       <c r="H4">
-        <v>0.1323356820945848</v>
+        <v>0.13233568209458479</v>
       </c>
       <c r="I4">
-        <v>0.1608112705228825</v>
+        <v>0.16081127052288249</v>
       </c>
       <c r="J4">
-        <v>0.2151976627637981</v>
+        <v>0.21519766276379809</v>
       </c>
       <c r="K4">
-        <v>0.2025654732733432</v>
+        <v>0.20256547327334321</v>
       </c>
       <c r="L4">
-        <v>0.1861188370693039</v>
+        <v>0.18611883706930391</v>
       </c>
       <c r="M4">
-        <v>0.16786760737215</v>
+        <v>0.16786760737215001</v>
       </c>
       <c r="N4">
         <v>0.1539304426377931</v>
       </c>
       <c r="O4">
-        <v>0.1752468822979795</v>
+        <v>0.17524688229797949</v>
       </c>
       <c r="P4">
-        <v>0.1923938879647691</v>
+        <v>0.19239388796476911</v>
       </c>
       <c r="Q4">
-        <v>0.16639274491095</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.16639274491094999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C5">
-        <v>-0.01058580548812448</v>
+        <v>-1.058580548812448E-2</v>
       </c>
       <c r="D5">
-        <v>-0.01195020407826721</v>
+        <v>-1.1950204078267209E-2</v>
       </c>
       <c r="E5">
-        <v>-0.01092817641875306</v>
+        <v>-1.092817641875306E-2</v>
       </c>
       <c r="F5">
-        <v>0.03599433803123119</v>
+        <v>3.5994338031231192E-2</v>
       </c>
       <c r="G5">
-        <v>0.06692828404015934</v>
+        <v>6.6928284040159339E-2</v>
       </c>
       <c r="H5">
-        <v>0.1881809860293567</v>
+        <v>0.18818098602935671</v>
       </c>
       <c r="I5">
-        <v>0.176539602084534</v>
+        <v>0.17653960208453401</v>
       </c>
       <c r="J5">
-        <v>0.1721258622542788</v>
+        <v>0.17212586225427881</v>
       </c>
       <c r="K5">
-        <v>0.2145098459510006</v>
+        <v>0.21450984595100059</v>
       </c>
       <c r="L5">
         <v>0.2429619052625667</v>
       </c>
       <c r="M5">
-        <v>0.2504456601717449</v>
+        <v>0.25044566017174491</v>
       </c>
       <c r="N5">
-        <v>0.267551077028011</v>
+        <v>0.26755107702801101</v>
       </c>
       <c r="O5">
-        <v>0.278497738351287</v>
+        <v>0.27849773835128699</v>
       </c>
       <c r="P5">
-        <v>0.2704086148559685</v>
+        <v>0.27040861485596851</v>
       </c>
       <c r="Q5">
-        <v>0.2515540457171818</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.25155404571718182</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C6">
-        <v>-0.008278865446521826</v>
+        <v>-8.2788654465218263E-3</v>
       </c>
       <c r="D6">
-        <v>-0.002728906079129696</v>
+        <v>-2.728906079129696E-3</v>
       </c>
       <c r="E6">
-        <v>0.01249729926868325</v>
+        <v>1.2497299268683249E-2</v>
       </c>
       <c r="F6">
-        <v>0.1307406461988742</v>
+        <v>0.13074064619887421</v>
       </c>
       <c r="G6">
         <v>0.1202995016215864</v>
@@ -692,126 +863,122 @@
         <v>0.2121708731287073</v>
       </c>
       <c r="J6">
-        <v>0.2516148930951265</v>
+        <v>0.25161489309512652</v>
       </c>
       <c r="K6">
-        <v>0.3246807391796839</v>
+        <v>0.32468073917968387</v>
       </c>
       <c r="L6">
         <v>0.3307294474309207</v>
       </c>
       <c r="M6">
-        <v>0.3409351265729076</v>
+        <v>0.34093512657290759</v>
       </c>
       <c r="N6">
-        <v>0.3709494672733369</v>
+        <v>0.37094946727333689</v>
       </c>
       <c r="O6">
-        <v>0.3565412605997142</v>
+        <v>0.35654126059971419</v>
       </c>
       <c r="P6">
-        <v>0.3294933395953824</v>
+        <v>0.32949333959538241</v>
       </c>
       <c r="Q6">
-        <v>0.3085032451058385</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_</t>
-        </is>
+        <v>0.30850324510583849</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C7">
-        <v>-0.01459363464881977</v>
+        <v>-1.459363464881977E-2</v>
       </c>
       <c r="D7">
-        <v>-0.04287177107040157</v>
+        <v>-4.2871771070401569E-2</v>
       </c>
       <c r="E7">
-        <v>-0.0006614909241805615</v>
+        <v>-6.6149092418056154E-4</v>
       </c>
       <c r="F7">
-        <v>-0.0153857196926997</v>
+        <v>-1.5385719692699701E-2</v>
       </c>
       <c r="G7">
-        <v>0.005045878505406574</v>
+        <v>5.0458785054065744E-3</v>
       </c>
       <c r="H7">
-        <v>0.082673918118463</v>
+        <v>8.2673918118463002E-2</v>
       </c>
       <c r="I7">
-        <v>0.2100961842672732</v>
+        <v>0.21009618426727319</v>
       </c>
       <c r="J7">
-        <v>0.2048854495391181</v>
+        <v>0.20488544953911811</v>
       </c>
       <c r="K7">
-        <v>0.2489181917997411</v>
+        <v>0.24891819179974109</v>
       </c>
       <c r="L7">
-        <v>0.2406771344214957</v>
+        <v>0.24067713442149569</v>
       </c>
       <c r="M7">
         <v>0.2358975450160303</v>
       </c>
       <c r="N7">
-        <v>0.1974328518141902</v>
+        <v>0.19743285181419021</v>
       </c>
       <c r="O7">
-        <v>0.1861169826056401</v>
+        <v>0.18611698260564011</v>
       </c>
       <c r="P7">
-        <v>0.2167583401647939</v>
+        <v>0.21675834016479389</v>
       </c>
       <c r="Q7">
-        <v>0.23158248447086</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+        <v>0.23158248447085999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C8">
-        <v>-0.01770245532978175</v>
+        <v>-1.7702455329781749E-2</v>
       </c>
       <c r="D8">
-        <v>-0.01550134662048054</v>
+        <v>-1.5501346620480539E-2</v>
       </c>
       <c r="E8">
-        <v>0.01486951413685942</v>
+        <v>1.486951413685942E-2</v>
       </c>
       <c r="F8">
-        <v>0.07887747027559734</v>
+        <v>7.8877470275597342E-2</v>
       </c>
       <c r="G8">
         <v>0.1126437177247137</v>
       </c>
       <c r="H8">
-        <v>0.1950826968387065</v>
+        <v>0.19508269683870649</v>
       </c>
       <c r="I8">
-        <v>0.218965658588668</v>
+        <v>0.21896565858866801</v>
       </c>
       <c r="J8">
-        <v>0.2595688453176865</v>
+        <v>0.25956884531768648</v>
       </c>
       <c r="K8">
-        <v>0.2583944974297642</v>
+        <v>0.25839449742976422</v>
       </c>
       <c r="L8">
         <v>0.2437669293418295</v>
       </c>
       <c r="M8">
-        <v>0.2132530962275472</v>
+        <v>0.21325309622754721</v>
       </c>
       <c r="N8">
         <v>0.2234111540760233</v>
@@ -823,102 +990,98 @@
         <v>0.2417990502463917</v>
       </c>
       <c r="Q8">
-        <v>0.2408324878323105</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.24083248783231051</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C9">
-        <v>-0.01894500606309215</v>
+        <v>-1.894500606309215E-2</v>
       </c>
       <c r="D9">
-        <v>-0.01488801593154682</v>
+        <v>-1.488801593154682E-2</v>
       </c>
       <c r="E9">
-        <v>0.0159107396418762</v>
+        <v>1.5910739641876202E-2</v>
       </c>
       <c r="F9">
-        <v>0.07893523268844846</v>
+        <v>7.8935232688448459E-2</v>
       </c>
       <c r="G9">
-        <v>0.1136405983812137</v>
+        <v>0.11364059838121369</v>
       </c>
       <c r="H9">
-        <v>0.2023111847816302</v>
+        <v>0.20231118478163021</v>
       </c>
       <c r="I9">
         <v>0.2294020418379541</v>
       </c>
       <c r="J9">
-        <v>0.2802982771977153</v>
+        <v>0.28029827719771527</v>
       </c>
       <c r="K9">
-        <v>0.2874994336882634</v>
+        <v>0.28749943368826342</v>
       </c>
       <c r="L9">
-        <v>0.3151356956485036</v>
+        <v>0.31513569564850358</v>
       </c>
       <c r="M9">
-        <v>0.3052428454625897</v>
+        <v>0.30524284546258967</v>
       </c>
       <c r="N9">
-        <v>0.3374091295820258</v>
+        <v>0.33740912958202579</v>
       </c>
       <c r="O9">
-        <v>0.3519657814703788</v>
+        <v>0.35196578147037882</v>
       </c>
       <c r="P9">
-        <v>0.3863739305755703</v>
+        <v>0.38637393057557029</v>
       </c>
       <c r="Q9">
-        <v>0.4115957023535393</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.41159570235353932</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C10">
-        <v>-0.01896079831400268</v>
+        <v>-1.8960798314002679E-2</v>
       </c>
       <c r="D10">
-        <v>-0.01650846024268559</v>
+        <v>-1.6508460242685589E-2</v>
       </c>
       <c r="E10">
-        <v>0.01461819727496072</v>
+        <v>1.461819727496072E-2</v>
       </c>
       <c r="F10">
-        <v>0.07689616587363762</v>
+        <v>7.6896165873637623E-2</v>
       </c>
       <c r="G10">
-        <v>0.1164554703440036</v>
+        <v>0.11645547034400359</v>
       </c>
       <c r="H10">
-        <v>0.2020719351002437</v>
+        <v>0.20207193510024371</v>
       </c>
       <c r="I10">
-        <v>0.2297742307379134</v>
+        <v>0.22977423073791339</v>
       </c>
       <c r="J10">
-        <v>0.2808756434326015</v>
+        <v>0.28087564343260152</v>
       </c>
       <c r="K10">
         <v>0.2887613283548659</v>
       </c>
       <c r="L10">
-        <v>0.3188911277877667</v>
+        <v>0.31889112778776668</v>
       </c>
       <c r="M10">
         <v>0.3096390470060017</v>
@@ -930,32 +1093,30 @@
         <v>0.3589835994539492</v>
       </c>
       <c r="P10">
-        <v>0.3957361302794515</v>
+        <v>0.39573613027945148</v>
       </c>
       <c r="Q10">
         <v>0.4199830641477596</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C11">
-        <v>-0.02143817481498404</v>
+        <v>-2.1438174814984039E-2</v>
       </c>
       <c r="D11">
-        <v>-0.02093120670621564</v>
+        <v>-2.0931206706215639E-2</v>
       </c>
       <c r="E11">
-        <v>0.01322897314502455</v>
+        <v>1.3228973145024549E-2</v>
       </c>
       <c r="F11">
-        <v>0.07360214482651938</v>
+        <v>7.3602144826519375E-2</v>
       </c>
       <c r="G11">
         <v>0.1153536868572328</v>
@@ -964,117 +1125,113 @@
         <v>0.2033488139553217</v>
       </c>
       <c r="I11">
-        <v>0.2307234668173505</v>
+        <v>0.23072346681735051</v>
       </c>
       <c r="J11">
-        <v>0.2778269933064527</v>
+        <v>0.27782699330645272</v>
       </c>
       <c r="K11">
-        <v>0.2880801798137382</v>
+        <v>0.28808017981373818</v>
       </c>
       <c r="L11">
-        <v>0.3119579792122686</v>
+        <v>0.31195797921226859</v>
       </c>
       <c r="M11">
-        <v>0.3107814663001719</v>
+        <v>0.31078146630017189</v>
       </c>
       <c r="N11">
-        <v>0.3356375103267433</v>
+        <v>0.33563751032674333</v>
       </c>
       <c r="O11">
         <v>0.3614814995800546</v>
       </c>
       <c r="P11">
-        <v>0.3819340104907415</v>
+        <v>0.38193401049074149</v>
       </c>
       <c r="Q11">
-        <v>0.3992782346222765</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.39927823462227652</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>27</v>
       </c>
       <c r="B12">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C12">
-        <v>-0.006993078941759737</v>
+        <v>-6.9930789417597368E-3</v>
       </c>
       <c r="D12">
-        <v>-0.004389743419747428</v>
+        <v>-4.3897434197474284E-3</v>
       </c>
       <c r="E12">
-        <v>0.003658309047304307</v>
+        <v>3.658309047304307E-3</v>
       </c>
       <c r="F12">
-        <v>0.02671441706342597</v>
+        <v>2.671441706342597E-2</v>
       </c>
       <c r="G12">
-        <v>0.08446075566165717</v>
+        <v>8.4460755661657172E-2</v>
       </c>
       <c r="H12">
-        <v>0.1692868650107424</v>
+        <v>0.16928686501074239</v>
       </c>
       <c r="I12">
-        <v>0.2419756643470533</v>
+        <v>0.24197566434705331</v>
       </c>
       <c r="J12">
         <v>0.2254068711597399</v>
       </c>
       <c r="K12">
-        <v>0.2767505582391614</v>
+        <v>0.27675055823916139</v>
       </c>
       <c r="L12">
-        <v>0.3065034945523804</v>
+        <v>0.30650349455238041</v>
       </c>
       <c r="M12">
-        <v>0.3153795882737281</v>
+        <v>0.31537958827372808</v>
       </c>
       <c r="N12">
-        <v>0.3183475123436486</v>
+        <v>0.31834751234364861</v>
       </c>
       <c r="O12">
         <v>0.3213028042408056</v>
       </c>
       <c r="P12">
-        <v>0.3174848604952056</v>
+        <v>0.31748486049520558</v>
       </c>
       <c r="Q12">
-        <v>0.2982950551345712</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-        </is>
+        <v>0.29829505513457122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C13">
-        <v>-0.00644950340730212</v>
+        <v>-6.4495034073021196E-3</v>
       </c>
       <c r="D13">
-        <v>-0.02486031459920713</v>
+        <v>-2.486031459920713E-2</v>
       </c>
       <c r="E13">
-        <v>-0.05122298030780179</v>
+        <v>-5.1222980307801792E-2</v>
       </c>
       <c r="F13">
-        <v>-0.04892078386781916</v>
+        <v>-4.8920783867819159E-2</v>
       </c>
       <c r="G13">
-        <v>0.04740629579494796</v>
+        <v>4.7406295794947963E-2</v>
       </c>
       <c r="H13">
-        <v>0.04077955735059501</v>
+        <v>4.0779557350595012E-2</v>
       </c>
       <c r="I13">
-        <v>0.08951760828557322</v>
+        <v>8.9517608285573216E-2</v>
       </c>
       <c r="J13">
         <v>0.1188659022416324</v>
@@ -1092,7 +1249,7 @@
         <v>0.1391516643741588</v>
       </c>
       <c r="O13">
-        <v>0.1709711472883298</v>
+        <v>0.17097114728832979</v>
       </c>
       <c r="P13">
         <v>0.1711935593300643</v>
@@ -1101,197 +1258,189 @@
         <v>0.1840822437905614</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
       </c>
       <c r="B14">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C14">
-        <v>-0.01246024278892808</v>
+        <v>-1.2460242788928081E-2</v>
       </c>
       <c r="D14">
-        <v>-0.03478829479872769</v>
+        <v>-3.4788294798727692E-2</v>
       </c>
       <c r="E14">
-        <v>0.0004953834753648056</v>
+        <v>4.9538347536480563E-4</v>
       </c>
       <c r="F14">
-        <v>-0.005407408683990156</v>
+        <v>-5.407408683990156E-3</v>
       </c>
       <c r="G14">
-        <v>0.01494079511988948</v>
+        <v>1.494079511988948E-2</v>
       </c>
       <c r="H14">
-        <v>0.08941568269639383</v>
+        <v>8.9415682696393828E-2</v>
       </c>
       <c r="I14">
-        <v>0.2209931771657052</v>
+        <v>0.22099317716570521</v>
       </c>
       <c r="J14">
-        <v>0.2193478147184975</v>
+        <v>0.21934781471849751</v>
       </c>
       <c r="K14">
-        <v>0.2620241396414174</v>
+        <v>0.26202413964141741</v>
       </c>
       <c r="L14">
-        <v>0.2697990409146278</v>
+        <v>0.26979904091462781</v>
       </c>
       <c r="M14">
-        <v>0.2781239217478091</v>
+        <v>0.27812392174780909</v>
       </c>
       <c r="N14">
-        <v>0.2839517249224913</v>
+        <v>0.28395172492249132</v>
       </c>
       <c r="O14">
         <v>0.3086411558386597</v>
       </c>
       <c r="P14">
-        <v>0.3367759281855011</v>
+        <v>0.33677592818550112</v>
       </c>
       <c r="Q14">
-        <v>0.3618898765439503</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.36188987654395027</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C15">
-        <v>-0.01141140206601647</v>
+        <v>-1.1411402066016469E-2</v>
       </c>
       <c r="D15">
-        <v>-0.03886047204015834</v>
+        <v>-3.8860472040158342E-2</v>
       </c>
       <c r="E15">
-        <v>-0.001680709717249999</v>
+        <v>-1.680709717249999E-3</v>
       </c>
       <c r="F15">
-        <v>-0.01254476549965073</v>
+        <v>-1.254476549965073E-2</v>
       </c>
       <c r="G15">
-        <v>0.002928173317103668</v>
+        <v>2.928173317103668E-3</v>
       </c>
       <c r="H15">
-        <v>0.07992235949489668</v>
+        <v>7.9922359494896678E-2</v>
       </c>
       <c r="I15">
-        <v>0.2142897688812268</v>
+        <v>0.21428976888122681</v>
       </c>
       <c r="J15">
-        <v>0.2127294719559527</v>
+        <v>0.21272947195595271</v>
       </c>
       <c r="K15">
-        <v>0.2594129048217959</v>
+        <v>0.25941290482179591</v>
       </c>
       <c r="L15">
-        <v>0.2663289837284046</v>
+        <v>0.26632898372840458</v>
       </c>
       <c r="M15">
         <v>0.2754982506607731</v>
       </c>
       <c r="N15">
-        <v>0.2845948088326579</v>
+        <v>0.28459480883265792</v>
       </c>
       <c r="O15">
-        <v>0.3166586766173697</v>
+        <v>0.31665867661736968</v>
       </c>
       <c r="P15">
-        <v>0.3468008345723099</v>
+        <v>0.34680083457230992</v>
       </c>
       <c r="Q15">
         <v>0.3822804011366836</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-        </is>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>31</v>
       </c>
       <c r="B16">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C16">
-        <v>-0.01084485295242823</v>
+        <v>-1.084485295242823E-2</v>
       </c>
       <c r="D16">
-        <v>-0.03796710115087615</v>
+        <v>-3.7967101150876148E-2</v>
       </c>
       <c r="E16">
-        <v>0.00145305282436196</v>
+        <v>1.45305282436196E-3</v>
       </c>
       <c r="F16">
-        <v>-0.007792823410780072</v>
+        <v>-7.7928234107800722E-3</v>
       </c>
       <c r="G16">
-        <v>0.01328808970543624</v>
+        <v>1.328808970543624E-2</v>
       </c>
       <c r="H16">
-        <v>0.0830220581376277</v>
+        <v>8.3022058137627697E-2</v>
       </c>
       <c r="I16">
-        <v>0.2203644470960331</v>
+        <v>0.22036444709603309</v>
       </c>
       <c r="J16">
         <v>0.2259720814182099</v>
       </c>
       <c r="K16">
-        <v>0.2603126981621136</v>
+        <v>0.26031269816211361</v>
       </c>
       <c r="L16">
-        <v>0.2710662653254359</v>
+        <v>0.27106626532543587</v>
       </c>
       <c r="M16">
-        <v>0.2781325674062665</v>
+        <v>0.27813256740626652</v>
       </c>
       <c r="N16">
         <v>0.2848111850966798</v>
       </c>
       <c r="O16">
-        <v>0.3161981899736754</v>
+        <v>0.31619818997367538</v>
       </c>
       <c r="P16">
-        <v>0.344484705173649</v>
+        <v>0.34448470517364899</v>
       </c>
       <c r="Q16">
-        <v>0.3797339149053957</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.37973391490539571</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>32</v>
       </c>
       <c r="B17">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C17">
-        <v>-0.01301788170250912</v>
+        <v>-1.3017881702509121E-2</v>
       </c>
       <c r="D17">
-        <v>-0.03800753161879215</v>
+        <v>-3.8007531618792147E-2</v>
       </c>
       <c r="E17">
-        <v>-0.003406759357914286</v>
+        <v>-3.406759357914286E-3</v>
       </c>
       <c r="F17">
-        <v>-0.01301853114207873</v>
+        <v>-1.3018531142078731E-2</v>
       </c>
       <c r="G17">
-        <v>-0.001535099611421246</v>
+        <v>-1.5350996114212459E-3</v>
       </c>
       <c r="H17">
-        <v>0.07436949451962127</v>
+        <v>7.4369494519621271E-2</v>
       </c>
       <c r="I17">
         <v>0.2063543593910348</v>
@@ -1300,99 +1449,95 @@
         <v>0.2085945119012069</v>
       </c>
       <c r="K17">
-        <v>0.2505337420247225</v>
+        <v>0.25053374202472251</v>
       </c>
       <c r="L17">
-        <v>0.2649434068202353</v>
+        <v>0.26494340682023532</v>
       </c>
       <c r="M17">
-        <v>0.2732018181493012</v>
+        <v>0.27320181814930122</v>
       </c>
       <c r="N17">
-        <v>0.2758795702498992</v>
+        <v>0.27587957024989918</v>
       </c>
       <c r="O17">
-        <v>0.3076945281960746</v>
+        <v>0.30769452819607462</v>
       </c>
       <c r="P17">
-        <v>0.3378832615935479</v>
+        <v>0.33788326159354792</v>
       </c>
       <c r="Q17">
-        <v>0.3776178100672024</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.37761781006720241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>33</v>
       </c>
       <c r="B18">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C18">
-        <v>-0.006379355668488977</v>
+        <v>-6.3793556684889766E-3</v>
       </c>
       <c r="D18">
-        <v>-0.003962350424465164</v>
+        <v>-3.9623504244651643E-3</v>
       </c>
       <c r="E18">
-        <v>-8.143809892894768E-05</v>
+        <v>-8.1438098928947677E-5</v>
       </c>
       <c r="F18">
-        <v>0.02420854724450911</v>
+        <v>2.4208547244509111E-2</v>
       </c>
       <c r="G18">
-        <v>0.08163178924274535</v>
+        <v>8.1631789242745348E-2</v>
       </c>
       <c r="H18">
-        <v>0.2233248708691958</v>
+        <v>0.22332487086919581</v>
       </c>
       <c r="I18">
-        <v>0.2067763946453818</v>
+        <v>0.20677639464538181</v>
       </c>
       <c r="J18">
         <v>0.2151922909017184</v>
       </c>
       <c r="K18">
-        <v>0.2587483353809074</v>
+        <v>0.25874833538090741</v>
       </c>
       <c r="L18">
-        <v>0.2868997476574405</v>
+        <v>0.28689974765744047</v>
       </c>
       <c r="M18">
-        <v>0.299772751541775</v>
+        <v>0.29977275154177502</v>
       </c>
       <c r="N18">
-        <v>0.3054784434573641</v>
+        <v>0.30547844345736408</v>
       </c>
       <c r="O18">
-        <v>0.3152271680945026</v>
+        <v>0.31522716809450257</v>
       </c>
       <c r="P18">
-        <v>0.3144376129995601</v>
+        <v>0.31443761299956008</v>
       </c>
       <c r="Q18">
-        <v>0.3021626275722329</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-        </is>
+        <v>0.30216262757223289</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>34</v>
       </c>
       <c r="B19">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C19">
-        <v>-0.0073391568964368</v>
+        <v>-7.3391568964368001E-3</v>
       </c>
       <c r="D19">
-        <v>0.001764002265679785</v>
+        <v>1.764002265679785E-3</v>
       </c>
       <c r="E19">
-        <v>0.0168483194513581</v>
+        <v>1.6848319451358101E-2</v>
       </c>
       <c r="F19">
         <v>0.117280109305181</v>
@@ -1401,111 +1546,107 @@
         <v>0.1423395120872368</v>
       </c>
       <c r="H19">
-        <v>0.2479725904107591</v>
+        <v>0.24797259041075909</v>
       </c>
       <c r="I19">
-        <v>0.2495917706489151</v>
+        <v>0.24959177064891511</v>
       </c>
       <c r="J19">
         <v>0.2824832563589042</v>
       </c>
       <c r="K19">
-        <v>0.3474649344865102</v>
+        <v>0.34746493448651022</v>
       </c>
       <c r="L19">
         <v>0.3719713267663799</v>
       </c>
       <c r="M19">
-        <v>0.3760039186844129</v>
+        <v>0.37600391868441291</v>
       </c>
       <c r="N19">
-        <v>0.3971031870670663</v>
+        <v>0.39710318706706632</v>
       </c>
       <c r="O19">
-        <v>0.3968845973186421</v>
+        <v>0.39688459731864212</v>
       </c>
       <c r="P19">
-        <v>0.3707843361800628</v>
+        <v>0.37078433618006279</v>
       </c>
       <c r="Q19">
-        <v>0.3566243506283377</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+        <v>0.35662435062833769</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>35</v>
       </c>
       <c r="B20">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C20">
-        <v>-0.01049259239488702</v>
+        <v>-1.0492592394887019E-2</v>
       </c>
       <c r="D20">
-        <v>-0.001512555096895758</v>
+        <v>-1.512555096895758E-3</v>
       </c>
       <c r="E20">
-        <v>0.0218291703955246</v>
+        <v>2.1829170395524601E-2</v>
       </c>
       <c r="F20">
-        <v>0.1138613834787195</v>
+        <v>0.11386138347871951</v>
       </c>
       <c r="G20">
-        <v>0.1703349984489617</v>
+        <v>0.17033499844896169</v>
       </c>
       <c r="H20">
-        <v>0.2728728918169027</v>
+        <v>0.27287289181690272</v>
       </c>
       <c r="I20">
-        <v>0.2728552213754191</v>
+        <v>0.27285522137541912</v>
       </c>
       <c r="J20">
         <v>0.3043182433396977</v>
       </c>
       <c r="K20">
-        <v>0.3703127964994452</v>
+        <v>0.37031279649944521</v>
       </c>
       <c r="L20">
-        <v>0.3853322332889448</v>
+        <v>0.38533223328894478</v>
       </c>
       <c r="M20">
-        <v>0.4016850301328931</v>
+        <v>0.40168503013289308</v>
       </c>
       <c r="N20">
-        <v>0.4433257654088195</v>
+        <v>0.44332576540881952</v>
       </c>
       <c r="O20">
-        <v>0.4364589266761953</v>
+        <v>0.43645892667619529</v>
       </c>
       <c r="P20">
-        <v>0.4272987094813824</v>
+        <v>0.42729870948138238</v>
       </c>
       <c r="Q20">
-        <v>0.4271519338770762</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.42715193387707617</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
       </c>
       <c r="B21">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C21">
-        <v>-0.008198168961043297</v>
+        <v>-8.1981689610432975E-3</v>
       </c>
       <c r="D21">
-        <v>-0.004885719418194168</v>
+        <v>-4.8857194181941678E-3</v>
       </c>
       <c r="E21">
-        <v>-0.004384706595812794</v>
+        <v>-4.3847065958127936E-3</v>
       </c>
       <c r="F21">
-        <v>0.00838056941985363</v>
+        <v>8.3805694198536302E-3</v>
       </c>
       <c r="G21">
         <v>0.1147145647673618</v>
@@ -1514,230 +1655,222 @@
         <v>0.1415461648920904</v>
       </c>
       <c r="I21">
-        <v>0.1774263072619774</v>
+        <v>0.17742630726197739</v>
       </c>
       <c r="J21">
         <v>0.2353686254562864</v>
       </c>
       <c r="K21">
-        <v>0.2444961291047877</v>
+        <v>0.24449612910478771</v>
       </c>
       <c r="L21">
-        <v>0.2857957694005643</v>
+        <v>0.28579576940056428</v>
       </c>
       <c r="M21">
-        <v>0.2979567455941827</v>
+        <v>0.29795674559418273</v>
       </c>
       <c r="N21">
-        <v>0.3092957055488761</v>
+        <v>0.30929570554887609</v>
       </c>
       <c r="O21">
-        <v>0.2996364601835712</v>
+        <v>0.29963646018357121</v>
       </c>
       <c r="P21">
-        <v>0.2903074011248462</v>
+        <v>0.29030740112484621</v>
       </c>
       <c r="Q21">
-        <v>0.2787739154243503</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.27877391542435032</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>37</v>
       </c>
       <c r="B22">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C22">
-        <v>-0.01068949362626029</v>
+        <v>-1.068949362626029E-2</v>
       </c>
       <c r="D22">
-        <v>-0.009035226990141618</v>
+        <v>-9.0352269901416184E-3</v>
       </c>
       <c r="E22">
-        <v>-0.01297880272276572</v>
+        <v>-1.297880272276572E-2</v>
       </c>
       <c r="F22">
-        <v>-0.0332938267144089</v>
+        <v>-3.3293826714408899E-2</v>
       </c>
       <c r="G22">
-        <v>0.05194247606369843</v>
+        <v>5.194247606369843E-2</v>
       </c>
       <c r="H22">
-        <v>0.04384278674658731</v>
+        <v>4.3842786746587308E-2</v>
       </c>
       <c r="I22">
-        <v>0.008972111062938151</v>
+        <v>8.9721110629381508E-3</v>
       </c>
       <c r="J22">
-        <v>0.005023554458400108</v>
+        <v>5.0235544584001082E-3</v>
       </c>
       <c r="K22">
-        <v>-0.04471812311067661</v>
+        <v>-4.4718123110676612E-2</v>
       </c>
       <c r="L22">
-        <v>-0.05720182734198553</v>
+        <v>-5.7201827341985527E-2</v>
       </c>
       <c r="M22">
-        <v>-0.0530597916260251</v>
+        <v>-5.3059791626025102E-2</v>
       </c>
       <c r="N22">
-        <v>-0.01417852419917898</v>
+        <v>-1.417852419917898E-2</v>
       </c>
       <c r="O22">
-        <v>-0.02737267587666346</v>
+        <v>-2.737267587666346E-2</v>
       </c>
       <c r="P22">
-        <v>-0.01820868382457679</v>
+        <v>-1.8208683824576789E-2</v>
       </c>
       <c r="Q22">
-        <v>-0.006415326443321281</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>-6.4153264433212806E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>38</v>
       </c>
       <c r="B23">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C23">
-        <v>0.008698219030985162</v>
+        <v>8.6982190309851624E-3</v>
       </c>
       <c r="D23">
-        <v>0.02443517263042441</v>
+        <v>2.4435172630424409E-2</v>
       </c>
       <c r="E23">
-        <v>0.08040488501298042</v>
+        <v>8.0404885012980418E-2</v>
       </c>
       <c r="F23">
-        <v>0.1608043795914604</v>
+        <v>0.16080437959146041</v>
       </c>
       <c r="G23">
-        <v>0.2646007664026808</v>
+        <v>0.26460076640268082</v>
       </c>
       <c r="H23">
-        <v>0.3318982015491421</v>
+        <v>0.33189820154914212</v>
       </c>
       <c r="I23">
-        <v>0.374493262558</v>
+        <v>0.37449326255799997</v>
       </c>
       <c r="J23">
-        <v>0.3867396382870538</v>
+        <v>0.38673963828705382</v>
       </c>
       <c r="K23">
-        <v>0.39422821153717</v>
+        <v>0.39422821153717003</v>
       </c>
       <c r="L23">
-        <v>0.3724672719601114</v>
+        <v>0.37246727196011142</v>
       </c>
       <c r="M23">
-        <v>0.3520413012088466</v>
+        <v>0.35204130120884658</v>
       </c>
       <c r="N23">
-        <v>0.3043416588124725</v>
+        <v>0.30434165881247249</v>
       </c>
       <c r="O23">
-        <v>0.2942421868612672</v>
+        <v>0.29424218686126719</v>
       </c>
       <c r="P23">
-        <v>0.3047772608316737</v>
+        <v>0.30477726083167372</v>
       </c>
       <c r="Q23">
-        <v>0.3165369280027163</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.31653692800271632</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>39</v>
       </c>
       <c r="B24">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C24">
-        <v>0.1309941755480727</v>
+        <v>0.13099417554807269</v>
       </c>
       <c r="D24">
-        <v>0.2683133492624382</v>
+        <v>0.26831334926243822</v>
       </c>
       <c r="E24">
-        <v>0.3750190145798962</v>
+        <v>0.37501901457989623</v>
       </c>
       <c r="F24">
-        <v>0.4857173234148829</v>
+        <v>0.48571732341488288</v>
       </c>
       <c r="G24">
-        <v>0.498689633728591</v>
+        <v>0.49868963372859099</v>
       </c>
       <c r="H24">
-        <v>0.488979497939496</v>
+        <v>0.48897949793949602</v>
       </c>
       <c r="I24">
-        <v>0.4722680558048789</v>
+        <v>0.47226805580487891</v>
       </c>
       <c r="J24">
-        <v>0.4366880123607479</v>
+        <v>0.43668801236074789</v>
       </c>
       <c r="K24">
-        <v>0.4036094878770711</v>
+        <v>0.40360948787707113</v>
       </c>
       <c r="L24">
-        <v>0.3823265160168661</v>
+        <v>0.38232651601686612</v>
       </c>
       <c r="M24">
         <v>0.3828768169710941</v>
       </c>
       <c r="N24">
-        <v>0.3539030411191978</v>
+        <v>0.35390304111919779</v>
       </c>
       <c r="O24">
-        <v>0.3149461564073994</v>
+        <v>0.31494615640739942</v>
       </c>
       <c r="P24">
         <v>0.3122865669519525</v>
       </c>
       <c r="Q24">
-        <v>0.3048136852344451</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.30481368523444508</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>40</v>
       </c>
       <c r="B25">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C25">
-        <v>0.2533079146097502</v>
+        <v>0.25330791460975022</v>
       </c>
       <c r="D25">
-        <v>0.4278745050105192</v>
+        <v>0.42787450501051921</v>
       </c>
       <c r="E25">
-        <v>0.4398591297989149</v>
+        <v>0.43985912979891489</v>
       </c>
       <c r="F25">
-        <v>0.4466995659519327</v>
+        <v>0.44669956595193272</v>
       </c>
       <c r="G25">
-        <v>0.4396863148385148</v>
+        <v>0.43968631483851478</v>
       </c>
       <c r="H25">
-        <v>0.4307706714576173</v>
+        <v>0.43077067145761733</v>
       </c>
       <c r="I25">
-        <v>0.3801095666554409</v>
+        <v>0.38010956665544088</v>
       </c>
       <c r="J25">
-        <v>0.3852392590488474</v>
+        <v>0.38523925904884743</v>
       </c>
       <c r="K25">
         <v>0.3728355868200085</v>
@@ -1746,13 +1879,13 @@
         <v>0.3512669182902759</v>
       </c>
       <c r="M25">
-        <v>0.3291916530477709</v>
+        <v>0.32919165304777093</v>
       </c>
       <c r="N25">
-        <v>0.2746881015463541</v>
+        <v>0.27468810154635409</v>
       </c>
       <c r="O25">
-        <v>0.2304986338218321</v>
+        <v>0.23049863382183211</v>
       </c>
       <c r="P25">
         <v>0.2005718195908025</v>
@@ -1761,163 +1894,157 @@
         <v>0.1735421408835941</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>41</v>
       </c>
       <c r="B26">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C26">
-        <v>0.1317646187728805</v>
+        <v>0.13176461877288051</v>
       </c>
       <c r="D26">
-        <v>0.3453118560216378</v>
+        <v>0.34531185602163778</v>
       </c>
       <c r="E26">
-        <v>0.4439946880274612</v>
+        <v>0.44399468802746123</v>
       </c>
       <c r="F26">
-        <v>0.4977309235647183</v>
+        <v>0.49773092356471832</v>
       </c>
       <c r="G26">
-        <v>0.5382725850239544</v>
+        <v>0.53827258502395436</v>
       </c>
       <c r="H26">
-        <v>0.5444796666313559</v>
+        <v>0.54447966663135594</v>
       </c>
       <c r="I26">
-        <v>0.5359106763553029</v>
+        <v>0.53591067635530287</v>
       </c>
       <c r="J26">
-        <v>0.5356873023266309</v>
+        <v>0.53568730232663087</v>
       </c>
       <c r="K26">
-        <v>0.5365581860641007</v>
+        <v>0.53655818606410066</v>
       </c>
       <c r="L26">
-        <v>0.548509815922012</v>
+        <v>0.54850981592201198</v>
       </c>
       <c r="M26">
-        <v>0.5319698423676709</v>
+        <v>0.53196984236767086</v>
       </c>
       <c r="N26">
-        <v>0.5041614376472627</v>
+        <v>0.50416143764726273</v>
       </c>
       <c r="O26">
         <v>0.4805364328712225</v>
       </c>
       <c r="P26">
-        <v>0.4525476559279327</v>
+        <v>0.45254765592793272</v>
       </c>
       <c r="Q26">
-        <v>0.44143989272664</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
-        </is>
+        <v>0.44143989272664003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>42</v>
       </c>
       <c r="B27">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C27">
-        <v>0.2184769965906943</v>
+        <v>0.21847699659069431</v>
       </c>
       <c r="D27">
-        <v>0.4682380035655636</v>
+        <v>0.46823800356556361</v>
       </c>
       <c r="E27">
-        <v>0.4976472553064366</v>
+        <v>0.49764725530643661</v>
       </c>
       <c r="F27">
-        <v>0.5271082858848808</v>
+        <v>0.52710828588488079</v>
       </c>
       <c r="G27">
-        <v>0.5392787438554871</v>
+        <v>0.53927874385548713</v>
       </c>
       <c r="H27">
-        <v>0.5511663766870504</v>
+        <v>0.55116637668705037</v>
       </c>
       <c r="I27">
-        <v>0.5580728784504398</v>
+        <v>0.55807287845043985</v>
       </c>
       <c r="J27">
         <v>0.5472394391719797</v>
       </c>
       <c r="K27">
-        <v>0.5317837175319425</v>
+        <v>0.53178371753194253</v>
       </c>
       <c r="L27">
         <v>0.5340269236205798</v>
       </c>
       <c r="M27">
-        <v>0.5089685644214398</v>
+        <v>0.50896856442143978</v>
       </c>
       <c r="N27">
-        <v>0.4804951907889479</v>
+        <v>0.48049519078894792</v>
       </c>
       <c r="O27">
-        <v>0.4544885951646016</v>
+        <v>0.45448859516460161</v>
       </c>
       <c r="P27">
-        <v>0.4317827650559301</v>
+        <v>0.43178276505593011</v>
       </c>
       <c r="Q27">
-        <v>0.4153126012582609</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-        </is>
+        <v>0.41531260125826092</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>43</v>
       </c>
       <c r="B28">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C28">
-        <v>-0.002118717788331763</v>
+        <v>-2.1187177883317631E-3</v>
       </c>
       <c r="D28">
-        <v>0.002989609743287356</v>
+        <v>2.989609743287356E-3</v>
       </c>
       <c r="E28">
-        <v>0.07210539126980688</v>
+        <v>7.2105391269806876E-2</v>
       </c>
       <c r="F28">
-        <v>0.09380928833706897</v>
+        <v>9.3809288337068975E-2</v>
       </c>
       <c r="G28">
         <v>0.1281218954632784</v>
       </c>
       <c r="H28">
-        <v>0.1427926128477419</v>
+        <v>0.14279261284774189</v>
       </c>
       <c r="I28">
-        <v>0.1569987385680608</v>
+        <v>0.15699873856806079</v>
       </c>
       <c r="J28">
-        <v>0.1578370926449076</v>
+        <v>0.15783709264490761</v>
       </c>
       <c r="K28">
         <v>0.1240600302424671</v>
       </c>
       <c r="L28">
-        <v>0.0700603573329735</v>
+        <v>7.00603573329735E-2</v>
       </c>
       <c r="M28">
-        <v>-0.01975201259176669</v>
+        <v>-1.9752012591766691E-2</v>
       </c>
       <c r="N28">
-        <v>-0.0925014164426945</v>
+        <v>-9.2501416442694495E-2</v>
       </c>
       <c r="O28">
-        <v>-0.08094014789139586</v>
+        <v>-8.0940147891395864E-2</v>
       </c>
       <c r="P28">
         <v>-0.1044783908800111</v>
@@ -1926,41 +2053,39 @@
         <v>-0.1720273832795077</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-        </is>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>44</v>
       </c>
       <c r="B29">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C29">
-        <v>-0.003816499886833553</v>
+        <v>-3.8164998868335529E-3</v>
       </c>
       <c r="D29">
-        <v>0.003053303049690829</v>
+        <v>3.053303049690829E-3</v>
       </c>
       <c r="E29">
-        <v>0.06598518323883343</v>
+        <v>6.5985183238833428E-2</v>
       </c>
       <c r="F29">
-        <v>0.09276912924113222</v>
+        <v>9.2769129241132217E-2</v>
       </c>
       <c r="G29">
-        <v>0.1460759231702836</v>
+        <v>0.14607592317028359</v>
       </c>
       <c r="H29">
-        <v>0.1720337345368093</v>
+        <v>0.17203373453680931</v>
       </c>
       <c r="I29">
         <v>0.2433057836987613</v>
       </c>
       <c r="J29">
-        <v>0.2099748699514724</v>
+        <v>0.20997486995147241</v>
       </c>
       <c r="K29">
-        <v>0.2187655029996605</v>
+        <v>0.21876550299966049</v>
       </c>
       <c r="L29">
         <v>0.2015281470317753</v>
@@ -1975,38 +2100,36 @@
         <v>0.1143191592876963</v>
       </c>
       <c r="P29">
-        <v>0.1057886322496197</v>
+        <v>0.10578863224961969</v>
       </c>
       <c r="Q29">
         <v>0.1028343453033119</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-        </is>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>45</v>
       </c>
       <c r="B30">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C30">
-        <v>0.0005787839110160387</v>
+        <v>5.7878391101603868E-4</v>
       </c>
       <c r="D30">
-        <v>0.03052478845381053</v>
+        <v>3.0524788453810531E-2</v>
       </c>
       <c r="E30">
-        <v>0.08401063749175594</v>
+        <v>8.4010637491755941E-2</v>
       </c>
       <c r="F30">
-        <v>0.09509396393056115</v>
+        <v>9.5093963930561146E-2</v>
       </c>
       <c r="G30">
         <v>0.1212320819850136</v>
       </c>
       <c r="H30">
-        <v>0.1418798110532173</v>
+        <v>0.14187981105321729</v>
       </c>
       <c r="I30">
         <v>0.147162449935824</v>
@@ -2015,221 +2138,213 @@
         <v>0.1189216284478934</v>
       </c>
       <c r="K30">
-        <v>0.05874993601499676</v>
+        <v>5.8749936014996763E-2</v>
       </c>
       <c r="L30">
-        <v>0.05169079104082582</v>
+        <v>5.1690791040825822E-2</v>
       </c>
       <c r="M30">
-        <v>0.04757004584285163</v>
+        <v>4.7570045842851627E-2</v>
       </c>
       <c r="N30">
-        <v>-0.01445309970657696</v>
+        <v>-1.4453099706576961E-2</v>
       </c>
       <c r="O30">
-        <v>-0.0651689102876875</v>
+        <v>-6.5168910287687495E-2</v>
       </c>
       <c r="P30">
-        <v>-0.06757348440970488</v>
+        <v>-6.7573484409704884E-2</v>
       </c>
       <c r="Q30">
         <v>-0.1234024481522254</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-        </is>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>46</v>
       </c>
       <c r="B31">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C31">
-        <v>0.0008250792345005345</v>
+        <v>8.2507923450053449E-4</v>
       </c>
       <c r="D31">
-        <v>0.02902683728589602</v>
+        <v>2.9026837285896018E-2</v>
       </c>
       <c r="E31">
-        <v>0.0857140980973478</v>
+        <v>8.5714098097347799E-2</v>
       </c>
       <c r="F31">
-        <v>0.09841648928828528</v>
+        <v>9.841648928828528E-2</v>
       </c>
       <c r="G31">
-        <v>0.1233500270842074</v>
+        <v>0.12335002708420741</v>
       </c>
       <c r="H31">
         <v>0.1483903482648001</v>
       </c>
       <c r="I31">
-        <v>0.1601812636155679</v>
+        <v>0.16018126361556789</v>
       </c>
       <c r="J31">
         <v>0.1566793362195931</v>
       </c>
       <c r="K31">
-        <v>0.150833472723079</v>
+        <v>0.15083347272307901</v>
       </c>
       <c r="L31">
-        <v>0.1630679058420191</v>
+        <v>0.16306790584201911</v>
       </c>
       <c r="M31">
-        <v>0.1759503863203518</v>
+        <v>0.17595038632035179</v>
       </c>
       <c r="N31">
-        <v>0.1589601430141789</v>
+        <v>0.15896014301417891</v>
       </c>
       <c r="O31">
-        <v>0.1380559180344176</v>
+        <v>0.13805591803441761</v>
       </c>
       <c r="P31">
-        <v>0.1542973094363579</v>
+        <v>0.15429730943635789</v>
       </c>
       <c r="Q31">
-        <v>0.1903649546131349</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-        </is>
+        <v>0.19036495461313491</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>47</v>
       </c>
       <c r="B32">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C32">
-        <v>-0.001949367040084615</v>
+        <v>-1.9493670400846149E-3</v>
       </c>
       <c r="D32">
-        <v>0.007562247036644577</v>
+        <v>7.5622470366445774E-3</v>
       </c>
       <c r="E32">
-        <v>0.07020964295893532</v>
+        <v>7.0209642958935323E-2</v>
       </c>
       <c r="F32">
-        <v>0.0992720111950989</v>
+        <v>9.9272011195098903E-2</v>
       </c>
       <c r="G32">
-        <v>0.1555806990446429</v>
+        <v>0.15558069904464289</v>
       </c>
       <c r="H32">
-        <v>0.1809910136174546</v>
+        <v>0.18099101361745459</v>
       </c>
       <c r="I32">
         <v>0.2483997755170663</v>
       </c>
       <c r="J32">
-        <v>0.2253800638401124</v>
+        <v>0.22538006384011239</v>
       </c>
       <c r="K32">
-        <v>0.2360431576214853</v>
+        <v>0.23604315762148531</v>
       </c>
       <c r="L32">
-        <v>0.2374163234167185</v>
+        <v>0.23741632341671851</v>
       </c>
       <c r="M32">
-        <v>0.2355842439377581</v>
+        <v>0.23558424393775809</v>
       </c>
       <c r="N32">
         <v>0.2340988277542356</v>
       </c>
       <c r="O32">
-        <v>0.23250646054865</v>
+        <v>0.23250646054865001</v>
       </c>
       <c r="P32">
-        <v>0.1819089249429637</v>
+        <v>0.18190892494296371</v>
       </c>
       <c r="Q32">
-        <v>0.1953683282097919</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-        </is>
+        <v>0.19536832820979191</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>48</v>
       </c>
       <c r="B33">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C33">
-        <v>-0.0007088304359976228</v>
+        <v>-7.088304359976228E-4</v>
       </c>
       <c r="D33">
-        <v>0.01035699437976124</v>
+        <v>1.0356994379761239E-2</v>
       </c>
       <c r="E33">
-        <v>0.07092783405582952</v>
+        <v>7.0927834055829517E-2</v>
       </c>
       <c r="F33">
         <v>0.1003724778804624</v>
       </c>
       <c r="G33">
-        <v>0.1546475840575048</v>
+        <v>0.15464758405750481</v>
       </c>
       <c r="H33">
-        <v>0.1775912206401127</v>
+        <v>0.17759122064011271</v>
       </c>
       <c r="I33">
         <v>0.2485640003193538</v>
       </c>
       <c r="J33">
-        <v>0.224172783394512</v>
+        <v>0.22417278339451199</v>
       </c>
       <c r="K33">
-        <v>0.2384819543041682</v>
+        <v>0.23848195430416819</v>
       </c>
       <c r="L33">
-        <v>0.2372048171765558</v>
+        <v>0.23720481717655581</v>
       </c>
       <c r="M33">
         <v>0.2395879611421248</v>
       </c>
       <c r="N33">
-        <v>0.2439099570043471</v>
+        <v>0.24390995700434709</v>
       </c>
       <c r="O33">
-        <v>0.2501086407438883</v>
+        <v>0.25010864074388828</v>
       </c>
       <c r="P33">
-        <v>0.2068917420217571</v>
+        <v>0.20689174202175711</v>
       </c>
       <c r="Q33">
-        <v>0.2258773056579174</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-        </is>
+        <v>0.22587730565791739</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>49</v>
       </c>
       <c r="B34">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C34">
-        <v>-0.001981430255147331</v>
+        <v>-1.981430255147331E-3</v>
       </c>
       <c r="D34">
-        <v>0.01046284762800623</v>
+        <v>1.0462847628006229E-2</v>
       </c>
       <c r="E34">
-        <v>0.07123799267574053</v>
+        <v>7.1237992675740533E-2</v>
       </c>
       <c r="F34">
-        <v>0.09875729652073124</v>
+        <v>9.8757296520731244E-2</v>
       </c>
       <c r="G34">
-        <v>0.1530375595850113</v>
+        <v>0.15303755958501131</v>
       </c>
       <c r="H34">
         <v>0.1792130686198366</v>
       </c>
       <c r="I34">
-        <v>0.2454311532489044</v>
+        <v>0.24543115324890441</v>
       </c>
       <c r="J34">
         <v>0.2203391439481599</v>
@@ -2241,111 +2356,107 @@
         <v>0.2352659234844611</v>
       </c>
       <c r="M34">
-        <v>0.2352732414953835</v>
+        <v>0.23527324149538351</v>
       </c>
       <c r="N34">
-        <v>0.2412450956798836</v>
+        <v>0.24124509567988359</v>
       </c>
       <c r="O34">
-        <v>0.2494093674651162</v>
+        <v>0.24940936746511619</v>
       </c>
       <c r="P34">
-        <v>0.206901337514688</v>
+        <v>0.20690133751468801</v>
       </c>
       <c r="Q34">
         <v>0.2298488510985002</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-        </is>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>50</v>
       </c>
       <c r="B35">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C35">
-        <v>-0.00233555170333049</v>
+        <v>-2.3355517033304901E-3</v>
       </c>
       <c r="D35">
-        <v>0.006425636415185414</v>
+        <v>6.425636415185414E-3</v>
       </c>
       <c r="E35">
-        <v>0.06925456596326204</v>
+        <v>6.9254565963262044E-2</v>
       </c>
       <c r="F35">
-        <v>0.09510601311525238</v>
+        <v>9.510601311525238E-2</v>
       </c>
       <c r="G35">
-        <v>0.1463567755898627</v>
+        <v>0.14635677558986271</v>
       </c>
       <c r="H35">
-        <v>0.1727962648525364</v>
+        <v>0.17279626485253641</v>
       </c>
       <c r="I35">
-        <v>0.24379079333266</v>
+        <v>0.24379079333265999</v>
       </c>
       <c r="J35">
-        <v>0.2236079825522543</v>
+        <v>0.22360798255225431</v>
       </c>
       <c r="K35">
         <v>0.2403990379540058</v>
       </c>
       <c r="L35">
-        <v>0.2418764996990529</v>
+        <v>0.24187649969905289</v>
       </c>
       <c r="M35">
-        <v>0.2438813491689898</v>
+        <v>0.24388134916898979</v>
       </c>
       <c r="N35">
-        <v>0.252777399113586</v>
+        <v>0.25277739911358599</v>
       </c>
       <c r="O35">
-        <v>0.2670493673105955</v>
+        <v>0.26704936731059548</v>
       </c>
       <c r="P35">
-        <v>0.2339359225606553</v>
+        <v>0.23393592256065529</v>
       </c>
       <c r="Q35">
-        <v>0.2634735118733373</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-        </is>
+        <v>0.26347351187333728</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>51</v>
       </c>
       <c r="B36">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C36">
-        <v>-0.0002484891274877963</v>
+        <v>-2.4848912748779632E-4</v>
       </c>
       <c r="D36">
-        <v>0.009911493744587512</v>
+        <v>9.9114937445875118E-3</v>
       </c>
       <c r="E36">
-        <v>0.07399873330667781</v>
+        <v>7.3998733306677805E-2</v>
       </c>
       <c r="F36">
-        <v>0.09748689933400971</v>
+        <v>9.7486899334009711E-2</v>
       </c>
       <c r="G36">
-        <v>0.1518057303436604</v>
+        <v>0.15180573034366041</v>
       </c>
       <c r="H36">
         <v>0.1765057843120344</v>
       </c>
       <c r="I36">
-        <v>0.2459658308488281</v>
+        <v>0.24596583084882809</v>
       </c>
       <c r="J36">
-        <v>0.2277151565739363</v>
+        <v>0.22771515657393629</v>
       </c>
       <c r="K36">
-        <v>0.2433963324628521</v>
+        <v>0.24339633246285211</v>
       </c>
       <c r="L36">
         <v>0.2412905330580197</v>
@@ -2354,368 +2465,354 @@
         <v>0.2361872025405394</v>
       </c>
       <c r="N36">
-        <v>0.2167074650840299</v>
+        <v>0.21670746508402991</v>
       </c>
       <c r="O36">
-        <v>0.1958874086982476</v>
+        <v>0.19588740869824761</v>
       </c>
       <c r="P36">
         <v>0.1535698802302487</v>
       </c>
       <c r="Q36">
-        <v>0.1638541038709412</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-        </is>
+        <v>0.16385410387094121</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>52</v>
       </c>
       <c r="B37">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C37">
-        <v>-0.001131944757303196</v>
+        <v>-1.131944757303196E-3</v>
       </c>
       <c r="D37">
-        <v>0.009615658839486039</v>
+        <v>9.6156588394860389E-3</v>
       </c>
       <c r="E37">
-        <v>0.06862085885635591</v>
+        <v>6.862085885635591E-2</v>
       </c>
       <c r="F37">
-        <v>0.09910439516702191</v>
+        <v>9.9104395167021908E-2</v>
       </c>
       <c r="G37">
-        <v>0.1545065097214416</v>
+        <v>0.15450650972144159</v>
       </c>
       <c r="H37">
-        <v>0.1768580292272567</v>
+        <v>0.17685802922725671</v>
       </c>
       <c r="I37">
-        <v>0.2491738565298195</v>
+        <v>0.24917385652981949</v>
       </c>
       <c r="J37">
-        <v>0.2244731739475399</v>
+        <v>0.22447317394753991</v>
       </c>
       <c r="K37">
-        <v>0.2380516865593068</v>
+        <v>0.23805168655930681</v>
       </c>
       <c r="L37">
-        <v>0.2374680677752193</v>
+        <v>0.23746806777521931</v>
       </c>
       <c r="M37">
         <v>0.2357115467166139</v>
       </c>
       <c r="N37">
-        <v>0.2220323100911596</v>
+        <v>0.22203231009115959</v>
       </c>
       <c r="O37">
-        <v>0.2045874236834981</v>
+        <v>0.20458742368349811</v>
       </c>
       <c r="P37">
-        <v>0.1645405771497102</v>
+        <v>0.16454057714971021</v>
       </c>
       <c r="Q37">
-        <v>0.1792441021927375</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-        </is>
+        <v>0.17924410219273751</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>53</v>
       </c>
       <c r="B38">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C38">
-        <v>-0.002102437056413251</v>
+        <v>-2.1024370564132512E-3</v>
       </c>
       <c r="D38">
-        <v>0.01008065260806955</v>
+        <v>1.008065260806955E-2</v>
       </c>
       <c r="E38">
-        <v>0.07162589811694403</v>
+        <v>7.1625898116944031E-2</v>
       </c>
       <c r="F38">
-        <v>0.09981006131764734</v>
+        <v>9.9810061317647344E-2</v>
       </c>
       <c r="G38">
-        <v>0.152430144987295</v>
+        <v>0.15243014498729501</v>
       </c>
       <c r="H38">
-        <v>0.1784713744412673</v>
+        <v>0.17847137444126729</v>
       </c>
       <c r="I38">
         <v>0.2458605066014202</v>
       </c>
       <c r="J38">
-        <v>0.2234284924598489</v>
+        <v>0.22342849245984889</v>
       </c>
       <c r="K38">
-        <v>0.2373068934085931</v>
+        <v>0.23730689340859309</v>
       </c>
       <c r="L38">
-        <v>0.2408048978447417</v>
+        <v>0.24080489784474171</v>
       </c>
       <c r="M38">
-        <v>0.2396680206538556</v>
+        <v>0.23966802065385559</v>
       </c>
       <c r="N38">
         <v>0.2220210781015208</v>
       </c>
       <c r="O38">
-        <v>0.2076045677058352</v>
+        <v>0.20760456770583521</v>
       </c>
       <c r="P38">
-        <v>0.1758524918557582</v>
+        <v>0.17585249185575819</v>
       </c>
       <c r="Q38">
-        <v>0.1859450368555434</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-        </is>
+        <v>0.18594503685554339</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>54</v>
       </c>
       <c r="B39">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C39">
-        <v>0.001974475178395556</v>
+        <v>1.974475178395556E-3</v>
       </c>
       <c r="D39">
-        <v>0.01298678635741008</v>
+        <v>1.2986786357410081E-2</v>
       </c>
       <c r="E39">
-        <v>0.0758958893843162</v>
+        <v>7.5895889384316198E-2</v>
       </c>
       <c r="F39">
         <v>0.1043518349184704</v>
       </c>
       <c r="G39">
-        <v>0.1567244080096477</v>
+        <v>0.15672440800964771</v>
       </c>
       <c r="H39">
-        <v>0.1802004922169597</v>
+        <v>0.18020049221695969</v>
       </c>
       <c r="I39">
-        <v>0.2564632783709282</v>
+        <v>0.25646327837092819</v>
       </c>
       <c r="J39">
         <v>0.2270701616365777</v>
       </c>
       <c r="K39">
-        <v>0.2403324037365339</v>
+        <v>0.24033240373653389</v>
       </c>
       <c r="L39">
-        <v>0.2448380399095886</v>
+        <v>0.24483803990958861</v>
       </c>
       <c r="M39">
-        <v>0.2453330548929341</v>
+        <v>0.24533305489293411</v>
       </c>
       <c r="N39">
-        <v>0.2341867044618492</v>
+        <v>0.23418670446184919</v>
       </c>
       <c r="O39">
-        <v>0.2235380347751398</v>
+        <v>0.22353803477513981</v>
       </c>
       <c r="P39">
-        <v>0.2011765964000216</v>
+        <v>0.20117659640002161</v>
       </c>
       <c r="Q39">
-        <v>0.2108849555581531</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-        </is>
+        <v>0.21088495555815309</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>55</v>
       </c>
       <c r="B40">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C40">
-        <v>-0.003992952804552641</v>
+        <v>-3.9929528045526408E-3</v>
       </c>
       <c r="D40">
-        <v>0.003028880970422887</v>
+        <v>3.0288809704228869E-3</v>
       </c>
       <c r="E40">
-        <v>0.06856226305894504</v>
+        <v>6.8562263058945042E-2</v>
       </c>
       <c r="F40">
-        <v>0.09228135950652973</v>
+        <v>9.2281359506529728E-2</v>
       </c>
       <c r="G40">
-        <v>0.1490693652788747</v>
+        <v>0.14906936527887471</v>
       </c>
       <c r="H40">
         <v>0.1738735282307258</v>
       </c>
       <c r="I40">
-        <v>0.2465835337003361</v>
+        <v>0.24658353370033609</v>
       </c>
       <c r="J40">
-        <v>0.2243247898360066</v>
+        <v>0.22432478983600659</v>
       </c>
       <c r="K40">
-        <v>0.2422378226296268</v>
+        <v>0.24223782262962679</v>
       </c>
       <c r="L40">
-        <v>0.2445408600894163</v>
+        <v>0.24454086008941631</v>
       </c>
       <c r="M40">
-        <v>0.251189787489582</v>
+        <v>0.25118978748958198</v>
       </c>
       <c r="N40">
-        <v>0.2517013297071424</v>
+        <v>0.25170132970714237</v>
       </c>
       <c r="O40">
-        <v>0.2578330333072468</v>
+        <v>0.25783303330724677</v>
       </c>
       <c r="P40">
         <v>0.2273434450517833</v>
       </c>
       <c r="Q40">
-        <v>0.2514925346992387</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-        </is>
+        <v>0.25149253469923871</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>56</v>
       </c>
       <c r="B41">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C41">
-        <v>0.02114386471603997</v>
+        <v>2.1143864716039969E-2</v>
       </c>
       <c r="D41">
-        <v>-0.000835167062825146</v>
+        <v>-8.3516706282514596E-4</v>
       </c>
       <c r="E41">
-        <v>0.06295247442718155</v>
+        <v>6.2952474427181548E-2</v>
       </c>
       <c r="F41">
-        <v>0.08808433493266392</v>
+        <v>8.8084334932663919E-2</v>
       </c>
       <c r="G41">
-        <v>0.08821821295123045</v>
+        <v>8.8218212951230446E-2</v>
       </c>
       <c r="H41">
-        <v>0.05157718238415615</v>
+        <v>5.1577182384156151E-2</v>
       </c>
       <c r="I41">
-        <v>-0.0536832180810048</v>
+        <v>-5.3683218081004798E-2</v>
       </c>
       <c r="J41">
-        <v>-0.1439893780300655</v>
+        <v>-0.14398937803006551</v>
       </c>
       <c r="K41">
-        <v>-0.1800567814888542</v>
+        <v>-0.18005678148885421</v>
       </c>
       <c r="L41">
-        <v>-0.2453045283986832</v>
+        <v>-0.24530452839868319</v>
       </c>
       <c r="M41">
-        <v>-0.2930363382389736</v>
+        <v>-0.29303633823897363</v>
       </c>
       <c r="N41">
-        <v>-0.3273605858690571</v>
+        <v>-0.32736058586905709</v>
       </c>
       <c r="O41">
-        <v>-0.3148563722478684</v>
+        <v>-0.31485637224786839</v>
       </c>
       <c r="P41">
-        <v>-0.2522105142994125</v>
+        <v>-0.25221051429941249</v>
       </c>
       <c r="Q41">
-        <v>-0.1865001197093684</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-        </is>
+        <v>-0.18650011970936839</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>57</v>
       </c>
       <c r="B42">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C42">
-        <v>0.02146762919940736</v>
+        <v>2.1467629199407361E-2</v>
       </c>
       <c r="D42">
-        <v>0.01775041110992763</v>
+        <v>1.775041110992763E-2</v>
       </c>
       <c r="E42">
-        <v>0.0916936893122127</v>
+        <v>9.1693689312212695E-2</v>
       </c>
       <c r="F42">
-        <v>0.1447441490403694</v>
+        <v>0.14474414904036939</v>
       </c>
       <c r="G42">
-        <v>0.147624551877107</v>
+        <v>0.14762455187710699</v>
       </c>
       <c r="H42">
         <v>0.1369942934244808</v>
       </c>
       <c r="I42">
-        <v>0.07627018885414595</v>
+        <v>7.6270188854145951E-2</v>
       </c>
       <c r="J42">
-        <v>0.02042762343463374</v>
+        <v>2.0427623434633741E-2</v>
       </c>
       <c r="K42">
-        <v>-0.002593539400282801</v>
+        <v>-2.593539400282801E-3</v>
       </c>
       <c r="L42">
-        <v>-0.0425291836354307</v>
+        <v>-4.2529183635430699E-2</v>
       </c>
       <c r="M42">
-        <v>-0.03721383783151218</v>
+        <v>-3.7213837831512178E-2</v>
       </c>
       <c r="N42">
-        <v>0.06450350745581677</v>
+        <v>6.4503507455816775E-2</v>
       </c>
       <c r="O42">
         <v>0.1182740399485939</v>
       </c>
       <c r="P42">
-        <v>0.1430971699969464</v>
+        <v>0.14309716999694641</v>
       </c>
       <c r="Q42">
         <v>0.1910674067087951</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-        </is>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>58</v>
       </c>
       <c r="B43">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C43">
-        <v>0.02161358500037608</v>
+        <v>2.1613585000376079E-2</v>
       </c>
       <c r="D43">
-        <v>0.02318571999902532</v>
+        <v>2.3185719999025321E-2</v>
       </c>
       <c r="E43">
-        <v>0.09614981515314709</v>
+        <v>9.6149815153147092E-2</v>
       </c>
       <c r="F43">
-        <v>0.1554528680783699</v>
+        <v>0.15545286807836989</v>
       </c>
       <c r="G43">
         <v>0.1551490973042865</v>
@@ -2724,123 +2821,119 @@
         <v>0.1489724685461446</v>
       </c>
       <c r="I43">
-        <v>0.1159902628911371</v>
+        <v>0.11599026289113711</v>
       </c>
       <c r="J43">
-        <v>0.08341466078866182</v>
+        <v>8.3414660788661818E-2</v>
       </c>
       <c r="K43">
-        <v>0.04104135582528071</v>
+        <v>4.1041355825280713E-2</v>
       </c>
       <c r="L43">
-        <v>0.06490446889702471</v>
+        <v>6.4904468897024711E-2</v>
       </c>
       <c r="M43">
-        <v>0.07345424268373943</v>
+        <v>7.3454242683739429E-2</v>
       </c>
       <c r="N43">
-        <v>0.1698246944029949</v>
+        <v>0.16982469440299491</v>
       </c>
       <c r="O43">
-        <v>0.1654812501018202</v>
+        <v>0.16548125010182019</v>
       </c>
       <c r="P43">
-        <v>0.2355797442476127</v>
+        <v>0.23557974424761269</v>
       </c>
       <c r="Q43">
-        <v>0.2982155697753963</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
+        <v>0.29821556977539632</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>59</v>
       </c>
       <c r="B44">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C44">
-        <v>0.03326053901472379</v>
+        <v>3.326053901472379E-2</v>
       </c>
       <c r="D44">
-        <v>-0.009280364714924792</v>
+        <v>-9.2803647149247923E-3</v>
       </c>
       <c r="E44">
-        <v>0.03967944763910691</v>
+        <v>3.9679447639106913E-2</v>
       </c>
       <c r="F44">
-        <v>0.06131663773215706</v>
+        <v>6.1316637732157057E-2</v>
       </c>
       <c r="G44">
-        <v>0.03215869832837926</v>
+        <v>3.2158698328379261E-2</v>
       </c>
       <c r="H44">
-        <v>-0.04630195020054381</v>
+        <v>-4.6301950200543812E-2</v>
       </c>
       <c r="I44">
-        <v>-0.09724688422658952</v>
+        <v>-9.7246884226589517E-2</v>
       </c>
       <c r="J44">
-        <v>-0.1210647991325566</v>
+        <v>-0.12106479913255661</v>
       </c>
       <c r="K44">
-        <v>-0.08622216668613342</v>
+        <v>-8.6222166686133417E-2</v>
       </c>
       <c r="L44">
-        <v>-0.1797382992063483</v>
+        <v>-0.17973829920634829</v>
       </c>
       <c r="M44">
-        <v>-0.1743407501433294</v>
+        <v>-0.17434075014332939</v>
       </c>
       <c r="N44">
         <v>-0.148309696885432</v>
       </c>
       <c r="O44">
-        <v>-0.1498855464363762</v>
+        <v>-0.14988554643637619</v>
       </c>
       <c r="P44">
-        <v>-0.09753519046466493</v>
+        <v>-9.7535190464664925E-2</v>
       </c>
       <c r="Q44">
-        <v>-0.04907935350458213</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
+        <v>-4.9079353504582132E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>60</v>
       </c>
       <c r="B45">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C45">
-        <v>0.005541376545656904</v>
+        <v>5.541376545656904E-3</v>
       </c>
       <c r="D45">
-        <v>0.02645629980715699</v>
+        <v>2.645629980715699E-2</v>
       </c>
       <c r="E45">
-        <v>0.06053451369596009</v>
+        <v>6.0534513695960093E-2</v>
       </c>
       <c r="F45">
-        <v>0.1026320452745872</v>
+        <v>0.10263204527458721</v>
       </c>
       <c r="G45">
         <v>0.1042751146444383</v>
       </c>
       <c r="H45">
-        <v>0.1565092163991253</v>
+        <v>0.15650921639912529</v>
       </c>
       <c r="I45">
-        <v>0.1560374509178871</v>
+        <v>0.15603745091788709</v>
       </c>
       <c r="J45">
-        <v>0.1874987802367347</v>
+        <v>0.18749878023673469</v>
       </c>
       <c r="K45">
-        <v>0.2019926245619612</v>
+        <v>0.20199262456196121</v>
       </c>
       <c r="L45">
         <v>0.2176033707461999</v>
@@ -2852,35 +2945,33 @@
         <v>0.179503319956235</v>
       </c>
       <c r="O45">
-        <v>0.1680552252973128</v>
+        <v>0.16805522529731279</v>
       </c>
       <c r="P45">
-        <v>0.1447951125179544</v>
+        <v>0.14479511251795441</v>
       </c>
       <c r="Q45">
         <v>0.1242927820900243</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>61</v>
       </c>
       <c r="B46">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C46">
-        <v>0.02270064602308335</v>
+        <v>2.2700646023083349E-2</v>
       </c>
       <c r="D46">
-        <v>0.07580782034893534</v>
+        <v>7.5807820348935337E-2</v>
       </c>
       <c r="E46">
-        <v>0.1959732829345525</v>
+        <v>0.19597328293455249</v>
       </c>
       <c r="F46">
-        <v>0.3353902863501259</v>
+        <v>0.33539028635012591</v>
       </c>
       <c r="G46">
         <v>0.3632890058278479</v>
@@ -2889,44 +2980,42 @@
         <v>0.3705478451006039</v>
       </c>
       <c r="I46">
-        <v>0.3765977011474749</v>
+        <v>0.37659770114747487</v>
       </c>
       <c r="J46">
-        <v>0.3579880134602932</v>
+        <v>0.35798801346029319</v>
       </c>
       <c r="K46">
-        <v>0.3446905347570274</v>
+        <v>0.34469053475702738</v>
       </c>
       <c r="L46">
-        <v>0.3131232658021333</v>
+        <v>0.31312326580213329</v>
       </c>
       <c r="M46">
-        <v>0.2498553008967694</v>
+        <v>0.24985530089676941</v>
       </c>
       <c r="N46">
-        <v>0.1727753667495762</v>
+        <v>0.17277536674957619</v>
       </c>
       <c r="O46">
-        <v>0.1402217390384158</v>
+        <v>0.14022173903841581</v>
       </c>
       <c r="P46">
-        <v>0.1287328293525629</v>
+        <v>0.12873282935256289</v>
       </c>
       <c r="Q46">
         <v>0.1221048416942839</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>62</v>
       </c>
       <c r="B47">
-        <v>-0.01261817174953506</v>
+        <v>-1.261817174953506E-2</v>
       </c>
       <c r="C47">
-        <v>0.03847016647805112</v>
+        <v>3.847016647805112E-2</v>
       </c>
       <c r="D47">
         <v>0.110579218123592</v>
@@ -2938,40 +3027,52 @@
         <v>0.2207906995340202</v>
       </c>
       <c r="G47">
-        <v>0.2807031660443668</v>
+        <v>0.28070316604436679</v>
       </c>
       <c r="H47">
-        <v>0.3234530482750481</v>
+        <v>0.32345304827504812</v>
       </c>
       <c r="I47">
-        <v>0.3651984082175375</v>
+        <v>0.36519840821753752</v>
       </c>
       <c r="J47">
-        <v>0.3723693436032212</v>
+        <v>0.37236934360322121</v>
       </c>
       <c r="K47">
-        <v>0.365176218868045</v>
+        <v>0.36517621886804502</v>
       </c>
       <c r="L47">
-        <v>0.3701004117579951</v>
+        <v>0.37010041175799507</v>
       </c>
       <c r="M47">
-        <v>0.3467903819327994</v>
+        <v>0.34679038193279937</v>
       </c>
       <c r="N47">
-        <v>0.2919118055846672</v>
+        <v>0.29191180558466723</v>
       </c>
       <c r="O47">
-        <v>0.2554717688157919</v>
+        <v>0.25547176881579192</v>
       </c>
       <c r="P47">
         <v>0.2173421900313994</v>
       </c>
       <c r="Q47">
-        <v>0.1627605495160477</v>
+        <v>0.16276054951604771</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:Q47">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>